--- a/artfynd/A 59921-2023 artfynd.xlsx
+++ b/artfynd/A 59921-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59921-2023 artfynd.xlsx
+++ b/artfynd/A 59921-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>70129190</v>
+        <v>70313595</v>
       </c>
       <c r="B2" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564823.1048044044</v>
+        <v>564823</v>
       </c>
       <c r="R2" t="n">
-        <v>6666493.422140179</v>
+        <v>6666493</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -756,22 +751,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-03-25</t>
+          <t>2018-04-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-03-25</t>
+          <t>2018-04-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,27 +781,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eric Nyström</t>
+          <t>Eric Fjärdsmans</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eric Nyström</t>
+          <t>Eric Fjärdsmans</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>70058651</v>
+        <v>70129190</v>
       </c>
       <c r="B3" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,26 +804,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -849,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564823.1048044044</v>
+        <v>564823</v>
       </c>
       <c r="R3" t="n">
-        <v>6666493.422140179</v>
+        <v>6666493</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,27 +869,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-03-20</t>
+          <t>2018-03-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-03-20</t>
+          <t>2018-03-25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Verkade vara sjuk</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,15 +899,138 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eric Nyström</t>
+          <t>Eric Fjärdsmans</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eric Nyström</t>
+          <t>Eric Fjärdsmans</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>70058651</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Myggbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>564823</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6666493</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-03-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-03-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Verkade vara sjuk</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Eric Fjärdsmans</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Eric Fjärdsmans</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59921-2023 artfynd.xlsx
+++ b/artfynd/A 59921-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70313595</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70129190</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1031,8 +1046,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70058651</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>